--- a/samples/premium-comparison/premium_sujet.xlsx
+++ b/samples/premium-comparison/premium_sujet.xlsx
@@ -23,7 +23,7 @@
     <t>Contexte</t>
   </si>
   <si>
-    <t>Une enseigne de sneakers exploite deux boutiques Premium de centre-ville de taille comparable. L'une réalise un chiffre d'affaires plusieurs fois supérieur à l'autre. La direction hésite : faut-il fermer la petite boutique (« elle est trop petite, c'est normal qu'elle vende moins »), ou bien y a-t-il un vrai problème d'exploitation ? Votre mission : décomposer l'écart de CA avec l'équation du commerce de détail — CA = trafic × taux de transformation × panier moyen — pour identifier le levier dominant, puis dire ce qui relève de la fréquentation (souvent subie) et ce qui est réellement pilotable par l'équipe.</t>
+    <t>Une enseigne de sneakers exploite deux magasins de type Premium de taille comparable. L'un réalise un chiffre d'affaires plusieurs fois supérieur à l'autre. La direction hésite : faut-il considérer que le plus faible est condamné par sa taille ou son emplacement, ou bien y a-t-il un vrai problème d'exploitation ? Votre mission : décomposer l'écart de CA avec l'équation du commerce de détail — CA = trafic × taux de transformation × panier moyen — pour identifier le levier dominant, puis distinguer ce qui relève de la fréquentation (souvent subie) et ce qui est réellement pilotable.</t>
   </si>
   <si>
     <t>Feuilles de données</t>
@@ -65,7 +65,7 @@
     <t>Reportez vos résultats dans la feuille « Sujet », colonne « reponse ».</t>
   </si>
   <si>
-    <t>Arrondissez les montants à 2 décimales, les taux à 2 décimales, les ratios à 2 décimales.</t>
+    <t>Arrondissez les montants à 2 décimales, les taux et ratios à 2 décimales.</t>
   </si>
   <si>
     <t>Pour les questions d'analyse, rédigez une réponse argumentée citant vos chiffres.</t>
@@ -149,7 +149,7 @@
     <t>magasins</t>
   </si>
   <si>
-    <t>Filtrer la colonne type sur Premium.</t>
+    <t>Filtrer la colonne type.</t>
   </si>
   <si>
     <t>facile</t>
@@ -224,7 +224,7 @@
     <t>Taux de transformation</t>
   </si>
   <si>
-    <t>Calculez le taux de transformation de chaque Premium = nombre de tickets ÷ trafic annuel estimé (en %).</t>
+    <t>Calculez le taux de transformation de chaque Premium = tickets ÷ trafic annuel estimé (en %).</t>
   </si>
   <si>
     <t>ventes_exam + magasins</t>
@@ -254,10 +254,10 @@
     <t>Décomposition de l'écart</t>
   </si>
   <si>
-    <t>Entre le Premium fort et le Premium faible, calculez les trois ratios (trafic_fort/trafic_faible, transfo_fort/transfo_faible, panier_fort/panier_faible). Vérifiez que leur produit ≈ ratio des CA. Quel levier pèse le plus dans l'écart ?</t>
-  </si>
-  <si>
-    <t>Faire les trois rapports et leur produit.</t>
+    <t>Entre le Premium fort et le Premium faible, calculez les trois ratios (trafic, transformation, panier). Vérifiez que leur produit ≈ ratio des CA. Quel levier pèse le plus dans l'écart ?</t>
+  </si>
+  <si>
+    <t>Faire les trois rapports fort/faible et leur produit.</t>
   </si>
   <si>
     <t>Q9</t>
@@ -308,7 +308,7 @@
     <t>Hypothèse 1 — fréquentation vs commercial</t>
   </si>
   <si>
-    <t>Hypothèse 1 : « l'écart vient surtout d'un déficit de fréquentation (trafic), plus que de la performance commerciale (transformation + panier) ». À partir des ratios de Q8, dites si elle tient : comparez le ratio de trafic au produit des ratios transformation × panier. Concluez sur ce qui est subi vs pilotable.</t>
+    <t>Hypothèse 1 : « l'écart vient surtout d'un déficit de fréquentation (trafic), plus que de la performance commerciale (transformation + panier) ». À partir des ratios de Q8, comparez le ratio de trafic au produit des ratios transformation × panier. Concluez sur ce qui est subi vs pilotable.</t>
   </si>
   <si>
     <t>Comparer ratio trafic et (ratio transfo × ratio panier).</t>
@@ -323,7 +323,7 @@
     <t>Hypothèse 2 — effet taille + recommandations</t>
   </si>
   <si>
-    <t>Hypothèse 2 : « le petit magasin vend moins simplement parce qu'il est plus petit ». Réfutez ou confirmez-la en comparant les surfaces (Q1) et les CA/m² (Q9) et CA/vendeur (Q10). Si l'écart persiste après normalisation, c'est une vraie sous-performance. Proposez deux actions de pilotage : une sur le levier dominant (Q12) et une sur un levier pilotable (transformation : formation/vente additionnelle ; ou panier : montée en gamme).</t>
+    <t>Hypothèse 2 : « le magasin faible vend moins simplement parce qu'il est plus petit ». Réfutez ou confirmez-la en comparant surfaces (Q1), CA/m² (Q9) et CA/vendeur (Q10). Si l'écart persiste après normalisation, c'est une vraie sous-performance. Proposez deux actions : une sur le levier dominant (Q12), une sur un levier pilotable (transformation : formation/vente additionnelle ; ou panier : montée en gamme).</t>
   </si>
   <si>
     <t>Q1 + Q9 + Q10</t>
